--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbRepo004MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbRepo004MTM.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\重庆\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
@@ -15,7 +10,7 @@
     <sheet name="数据" sheetId="1" r:id="rId1"/>
     <sheet name="参考格式" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,9 +42,6 @@
   </si>
   <si>
     <t>投资目的</t>
-  </si>
-  <si>
-    <t>证券账户</t>
   </si>
   <si>
     <t>备注</t>
@@ -244,8 +236,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -520,7 +515,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -528,52 +523,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.125" customWidth="1"/>
-    <col min="2" max="20" width="14.625" customWidth="1"/>
-    <col min="21" max="21" width="33" customWidth="1"/>
-    <col min="22" max="26" width="14.625" customWidth="1"/>
+    <col min="2" max="19" width="14.625" customWidth="1"/>
+    <col min="20" max="20" width="33" customWidth="1"/>
+    <col min="21" max="25" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" t="s">
-        <v>48</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
       </c>
       <c r="I1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" t="s">
         <v>53</v>
-      </c>
-      <c r="J1" t="s">
-        <v>54</v>
       </c>
       <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" t="s">
-        <v>8</v>
-      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -585,31 +581,31 @@
           <x14:formula1>
             <xm:f>参考格式!$B$2:$B$31</xm:f>
           </x14:formula1>
-          <xm:sqref>N2:N101</xm:sqref>
+          <xm:sqref>M2:M101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$C$2:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>Q2:Q101 H2:H101</xm:sqref>
+          <xm:sqref>P2:P101 H2:H101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$D$2:$D$3</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P101 F2:F101</xm:sqref>
+          <xm:sqref>O2:O101 F2:F101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>U2:U101</xm:sqref>
+          <xm:sqref>T2:T101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$G$2:$G$7</xm:f>
           </x14:formula1>
-          <xm:sqref>V2:V101</xm:sqref>
+          <xm:sqref>U2:U101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -655,182 +651,182 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbRepo004MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbRepo004MTM.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git\gztams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
@@ -20,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -190,6 +195,10 @@
   </si>
   <si>
     <t>回购期限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>质押券库</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -515,7 +524,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -523,16 +532,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.125" customWidth="1"/>
-    <col min="2" max="19" width="14.625" customWidth="1"/>
-    <col min="20" max="20" width="33" customWidth="1"/>
-    <col min="21" max="25" width="14.625" customWidth="1"/>
+    <col min="2" max="20" width="14.625" customWidth="1"/>
+    <col min="21" max="21" width="33" customWidth="1"/>
+    <col min="22" max="26" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -564,10 +573,13 @@
         <v>53</v>
       </c>
       <c r="K1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
@@ -581,31 +593,31 @@
           <x14:formula1>
             <xm:f>参考格式!$B$2:$B$31</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M101</xm:sqref>
+          <xm:sqref>N2:N101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$C$2:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P101 H2:H101</xm:sqref>
+          <xm:sqref>Q2:Q101 H2:H101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$D$2:$D$3</xm:f>
           </x14:formula1>
-          <xm:sqref>O2:O101 F2:F101</xm:sqref>
+          <xm:sqref>P2:P101 F2:F101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>T2:T101</xm:sqref>
+          <xm:sqref>U2:U101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$G$2:$G$7</xm:f>
           </x14:formula1>
-          <xm:sqref>U2:U101</xm:sqref>
+          <xm:sqref>V2:V101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
